--- a/nextflow/projects/Manish_22Rv1_Xeno2/Manish_22Rv1_Xeno2_metadata.xlsx
+++ b/nextflow/projects/Manish_22Rv1_Xeno2/Manish_22Rv1_Xeno2_metadata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cedarssinai-my.sharepoint.com/personal/saravanakumar_kailasammani_cshs_org/Documents/Desktop/Collaboration projects data/Manish_22RV1_Xenograft_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kailasamms\AppData\Local\Temp\editor-00aa220e-0453-4a41-8541-e33aea163788\hpc\home\kailasamms\scripts\nextflow\projects\Manish_22Rv1_Xeno2\1614429831\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="377" documentId="11_F25DC773A252ABDACC1048F619D84C565ADE58FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{335AED57-3A9F-4850-82B7-281467FAAF76}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E23BDB-5C1A-4AA2-B6E7-ACC158A2BB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="37">
   <si>
     <t>Condition</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>22Rv1</t>
+  </si>
+  <si>
+    <t>MT6_dup</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -811,6 +814,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1">
+        <v>199</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
